--- a/pandas.xlsx
+++ b/pandas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="965">
   <si>
     <t>Series</t>
   </si>
@@ -23013,18 +23013,190 @@
       </rPr>
       <t xml:space="preserve"> to keep only rows where Статус is "OK" or "Частична наличност", then reset the row numbering to start clean from 0, and throw away the old index.</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Keep ALL original rows + add a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>new column 'book_count</t>
+    </r>
+  </si>
+  <si>
+    <t>It reduces the data: One row per group (author)</t>
+  </si>
+  <si>
+    <r>
+      <t>df['</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>book_count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'] = df.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('author')['id'].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>transform</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('count')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df.groupby('</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>author</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>')['</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>aggregation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="56">
+  <fonts count="57">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23654,8 +23826,8 @@
   </cellStyleXfs>
   <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -23665,160 +23837,158 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -23831,16 +24001,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -23849,10 +24021,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FF179A77"/>
+      <color rgb="FFA47A20"/>
       <color rgb="FF64AF8C"/>
-      <color rgb="FF179A77"/>
       <color rgb="FFDA7BB9"/>
-      <color rgb="FFA47A20"/>
       <color rgb="FFA626A4"/>
       <color rgb="FFFF33CC"/>
       <color rgb="FF1E7D6A"/>
@@ -30147,25 +30319,25 @@
       <c r="E445" s="26" t="s">
         <v>939</v>
       </c>
-      <c r="F445" s="138" t="s">
+      <c r="F445" s="136" t="s">
         <v>939</v>
       </c>
-      <c r="G445" s="138" t="s">
+      <c r="G445" s="136" t="s">
         <v>939</v>
       </c>
-      <c r="H445" s="139" t="s">
+      <c r="H445" s="137" t="s">
         <v>939</v>
       </c>
       <c r="J445" s="26" t="s">
         <v>939</v>
       </c>
-      <c r="K445" s="138" t="s">
+      <c r="K445" s="136" t="s">
         <v>939</v>
       </c>
-      <c r="L445" s="138" t="s">
+      <c r="L445" s="136" t="s">
         <v>939</v>
       </c>
-      <c r="M445" s="139" t="s">
+      <c r="M445" s="137" t="s">
         <v>939</v>
       </c>
     </row>
@@ -30176,25 +30348,25 @@
       <c r="E446" s="9">
         <v>9541</v>
       </c>
-      <c r="F446" s="140" t="s">
+      <c r="F446" s="138" t="s">
         <v>939</v>
       </c>
-      <c r="G446" s="140" t="s">
+      <c r="G446" s="138" t="s">
         <v>939</v>
       </c>
-      <c r="H446" s="141" t="s">
+      <c r="H446" s="139" t="s">
         <v>939</v>
       </c>
       <c r="J446" s="9">
         <v>9541</v>
       </c>
-      <c r="K446" s="140" t="s">
+      <c r="K446" s="138" t="s">
         <v>939</v>
       </c>
-      <c r="L446" s="140" t="s">
+      <c r="L446" s="138" t="s">
         <v>939</v>
       </c>
-      <c r="M446" s="141" t="s">
+      <c r="M446" s="139" t="s">
         <v>939</v>
       </c>
     </row>
@@ -30226,7 +30398,7 @@
       <c r="B452" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="K452" s="137" t="s">
+      <c r="K452" s="135" t="s">
         <v>941</v>
       </c>
     </row>
@@ -30248,7 +30420,7 @@
       <c r="B455" s="84" t="s">
         <v>521</v>
       </c>
-      <c r="K455" s="137" t="s">
+      <c r="K455" s="135" t="s">
         <v>942</v>
       </c>
     </row>
@@ -30286,7 +30458,7 @@
       <c r="B466" s="75" t="s">
         <v>429</v>
       </c>
-      <c r="I466" s="137" t="s">
+      <c r="I466" s="135" t="s">
         <v>500</v>
       </c>
     </row>
@@ -30488,19 +30660,19 @@
       <c r="F486" s="7"/>
       <c r="G486" s="8"/>
       <c r="K486" s="22"/>
-      <c r="L486" s="131" t="s">
+      <c r="L486" s="129" t="s">
         <v>946</v>
       </c>
-      <c r="M486" s="131" t="s">
+      <c r="M486" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="N486" s="131" t="s">
+      <c r="N486" s="129" t="s">
         <v>952</v>
       </c>
-      <c r="O486" s="131" t="s">
+      <c r="O486" s="129" t="s">
         <v>949</v>
       </c>
-      <c r="P486" s="131" t="s">
+      <c r="P486" s="129" t="s">
         <v>950</v>
       </c>
     </row>
@@ -30566,19 +30738,19 @@
       </c>
     </row>
     <row r="492" spans="2:16">
-      <c r="K492" s="142" t="s">
+      <c r="K492" s="140" t="s">
         <v>946</v>
       </c>
-      <c r="L492" s="143" t="s">
+      <c r="L492" s="141" t="s">
         <v>947</v>
       </c>
-      <c r="M492" s="143" t="s">
+      <c r="M492" s="141" t="s">
         <v>948</v>
       </c>
-      <c r="N492" s="143" t="s">
+      <c r="N492" s="141" t="s">
         <v>949</v>
       </c>
-      <c r="O492" s="143" t="s">
+      <c r="O492" s="141" t="s">
         <v>950</v>
       </c>
     </row>
@@ -30586,19 +30758,19 @@
       <c r="B493" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="K493" s="142">
+      <c r="K493" s="140">
         <v>1</v>
       </c>
-      <c r="L493" s="142" t="s">
+      <c r="L493" s="140" t="s">
         <v>431</v>
       </c>
-      <c r="M493" s="142">
+      <c r="M493" s="140">
         <v>340</v>
       </c>
-      <c r="N493" s="142">
+      <c r="N493" s="140">
         <v>338</v>
       </c>
-      <c r="O493" s="142" t="s">
+      <c r="O493" s="140" t="s">
         <v>951</v>
       </c>
     </row>
@@ -30606,19 +30778,19 @@
       <c r="B494" s="75" t="s">
         <v>442</v>
       </c>
-      <c r="K494" s="142">
+      <c r="K494" s="140">
         <v>2</v>
       </c>
-      <c r="L494" s="142" t="s">
+      <c r="L494" s="140" t="s">
         <v>937</v>
       </c>
-      <c r="M494" s="142">
+      <c r="M494" s="140">
         <v>40</v>
       </c>
-      <c r="N494" s="142">
+      <c r="N494" s="140">
         <v>358</v>
       </c>
-      <c r="O494" s="142" t="s">
+      <c r="O494" s="140" t="s">
         <v>951</v>
       </c>
     </row>
@@ -30637,7 +30809,7 @@
       <c r="B500" s="75" t="s">
         <v>448</v>
       </c>
-      <c r="L500" s="145" t="s">
+      <c r="L500" s="143" t="s">
         <v>959</v>
       </c>
     </row>
@@ -30656,19 +30828,19 @@
     </row>
     <row r="503" spans="2:17">
       <c r="L503" s="22"/>
-      <c r="M503" s="144" t="s">
+      <c r="M503" s="142" t="s">
         <v>946</v>
       </c>
-      <c r="N503" s="131" t="s">
+      <c r="N503" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="O503" s="131" t="s">
+      <c r="O503" s="129" t="s">
         <v>952</v>
       </c>
-      <c r="P503" s="131" t="s">
+      <c r="P503" s="129" t="s">
         <v>949</v>
       </c>
-      <c r="Q503" s="131" t="s">
+      <c r="Q503" s="129" t="s">
         <v>950</v>
       </c>
     </row>
@@ -30918,16 +31090,16 @@
     </row>
     <row r="528" spans="2:15">
       <c r="K528" s="22"/>
-      <c r="L528" s="144" t="s">
+      <c r="L528" s="142" t="s">
         <v>946</v>
       </c>
-      <c r="M528" s="131" t="s">
+      <c r="M528" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="N528" s="131" t="s">
+      <c r="N528" s="129" t="s">
         <v>954</v>
       </c>
-      <c r="O528" s="131" t="s">
+      <c r="O528" s="129" t="s">
         <v>955</v>
       </c>
     </row>
@@ -37138,7 +37310,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="116"/>
-      <c r="B126" s="128" t="s">
+      <c r="B126" s="126" t="s">
         <v>604</v>
       </c>
     </row>
@@ -37147,7 +37319,7 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="116"/>
-      <c r="B128" s="128" t="s">
+      <c r="B128" s="126" t="s">
         <v>264</v>
       </c>
     </row>
@@ -37187,7 +37359,7 @@
       </c>
       <c r="I132" s="7"/>
       <c r="J132" s="8"/>
-      <c r="L132" s="129" t="s">
+      <c r="L132" s="127" t="s">
         <v>856</v>
       </c>
     </row>
@@ -37202,7 +37374,7 @@
       </c>
     </row>
     <row r="134" spans="1:12">
-      <c r="B134" s="128" t="s">
+      <c r="B134" s="126" t="s">
         <v>266</v>
       </c>
       <c r="H134" s="6" t="s">
@@ -37225,7 +37397,7 @@
       </c>
     </row>
     <row r="136" spans="1:12">
-      <c r="B136" s="128" t="s">
+      <c r="B136" s="126" t="s">
         <v>865</v>
       </c>
       <c r="H136" s="6" t="s">
@@ -37287,7 +37459,7 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="116"/>
-      <c r="B144" s="128" t="s">
+      <c r="B144" s="126" t="s">
         <v>875</v>
       </c>
       <c r="G144" t="s">
@@ -37296,7 +37468,7 @@
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="116"/>
-      <c r="B145" s="128" t="s">
+      <c r="B145" s="126" t="s">
         <v>884</v>
       </c>
       <c r="F145" t="s">
@@ -37308,7 +37480,7 @@
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="116"/>
-      <c r="B146" s="128" t="s">
+      <c r="B146" s="126" t="s">
         <v>886</v>
       </c>
       <c r="G146" t="s">
@@ -37324,7 +37496,7 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="116"/>
-      <c r="B149" s="128" t="s">
+      <c r="B149" s="126" t="s">
         <v>604</v>
       </c>
     </row>
@@ -37333,7 +37505,7 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="116"/>
-      <c r="B151" s="128" t="s">
+      <c r="B151" s="126" t="s">
         <v>264</v>
       </c>
     </row>
@@ -37414,7 +37586,7 @@
       </c>
     </row>
     <row r="158" spans="1:13">
-      <c r="B158" s="128" t="s">
+      <c r="B158" s="126" t="s">
         <v>266</v>
       </c>
       <c r="I158" s="9" t="s">
@@ -37427,7 +37599,7 @@
       </c>
     </row>
     <row r="160" spans="1:13">
-      <c r="B160" s="128" t="s">
+      <c r="B160" s="126" t="s">
         <v>885</v>
       </c>
     </row>
@@ -37588,7 +37760,7 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="23"/>
-      <c r="B191" s="128" t="s">
+      <c r="B191" s="126" t="s">
         <v>604</v>
       </c>
     </row>
@@ -37597,7 +37769,7 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="23"/>
-      <c r="B193" s="128" t="s">
+      <c r="B193" s="126" t="s">
         <v>264</v>
       </c>
     </row>
@@ -37612,11 +37784,11 @@
       <c r="B195" t="s">
         <v>921</v>
       </c>
-      <c r="I195" s="130" t="s">
+      <c r="I195" s="128" t="s">
         <v>917</v>
       </c>
       <c r="J195" s="15"/>
-      <c r="K195" s="131" t="s">
+      <c r="K195" s="129" t="s">
         <v>887</v>
       </c>
     </row>
@@ -37626,13 +37798,13 @@
         <v>920</v>
       </c>
       <c r="H196" s="2"/>
-      <c r="I196" s="132" t="s">
+      <c r="I196" s="130" t="s">
         <v>915</v>
       </c>
-      <c r="J196" s="132" t="s">
+      <c r="J196" s="130" t="s">
         <v>916</v>
       </c>
-      <c r="K196" s="132" t="s">
+      <c r="K196" s="130" t="s">
         <v>918</v>
       </c>
     </row>
@@ -37653,18 +37825,18 @@
       <c r="H198" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="I198" s="135">
+      <c r="I198" s="133">
         <v>63</v>
       </c>
-      <c r="J198" s="133">
+      <c r="J198" s="131">
         <v>31.5</v>
       </c>
-      <c r="K198" s="134">
+      <c r="K198" s="132">
         <v>30</v>
       </c>
     </row>
     <row r="199" spans="1:11">
-      <c r="B199" s="128" t="s">
+      <c r="B199" s="126" t="s">
         <v>266</v>
       </c>
       <c r="H199" s="2" t="s">
@@ -37695,7 +37867,7 @@
       </c>
     </row>
     <row r="201" spans="1:11">
-      <c r="B201" s="128" t="s">
+      <c r="B201" s="126" t="s">
         <v>919</v>
       </c>
       <c r="H201" s="2" t="s">
@@ -37753,17 +37925,17 @@
       </c>
     </row>
     <row r="211" spans="1:9">
-      <c r="A211" s="136" t="s">
+      <c r="A211" s="134" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="213" spans="1:9">
-      <c r="B213" s="128" t="s">
+      <c r="B213" s="126" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="215" spans="1:9">
-      <c r="B215" s="128" t="s">
+      <c r="B215" s="126" t="s">
         <v>264</v>
       </c>
     </row>
@@ -37805,7 +37977,7 @@
       <c r="I220" s="8"/>
     </row>
     <row r="221" spans="1:9">
-      <c r="B221" s="128" t="s">
+      <c r="B221" s="126" t="s">
         <v>266</v>
       </c>
       <c r="G221" s="6" t="s">
@@ -37822,7 +37994,7 @@
       <c r="I222" s="8"/>
     </row>
     <row r="223" spans="1:9">
-      <c r="B223" s="136" t="s">
+      <c r="B223" s="134" t="s">
         <v>757</v>
       </c>
       <c r="G223" s="6" t="s">
@@ -37832,7 +38004,7 @@
       <c r="I223" s="8"/>
     </row>
     <row r="224" spans="1:9">
-      <c r="B224" s="136" t="s">
+      <c r="B224" s="134" t="s">
         <v>933</v>
       </c>
       <c r="G224" s="9" t="s">
@@ -37906,7 +38078,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:Q17"/>
+  <dimension ref="A4:Q19"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.88671875" customWidth="1"/>
@@ -38179,23 +38351,23 @@
       <c r="A15" s="85">
         <v>9</v>
       </c>
-      <c r="B15" s="126" t="s">
+      <c r="B15" s="125" t="s">
         <v>841</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="127" t="s">
+      <c r="E15" s="145" t="s">
         <v>840</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126" t="s">
+      <c r="H15" s="125"/>
+      <c r="I15" s="125" t="s">
         <v>853</v>
       </c>
-      <c r="J15" s="126"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="126" t="s">
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125" t="s">
         <v>11</v>
       </c>
       <c r="M15" s="4"/>
@@ -38214,7 +38386,7 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="125" t="s">
+      <c r="E16" s="144" t="s">
         <v>842</v>
       </c>
       <c r="F16" s="7"/>
@@ -38255,6 +38427,25 @@
       <c r="N17" s="10"/>
       <c r="O17" s="11"/>
     </row>
+    <row r="18" spans="1:15">
+      <c r="E18" s="144" t="s">
+        <v>963</v>
+      </c>
+      <c r="I18" t="s">
+        <v>964</v>
+      </c>
+      <c r="L18" s="122" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="E19" s="144" t="s">
+        <v>962</v>
+      </c>
+      <c r="L19" t="s">
+        <v>960</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pandas.xlsx
+++ b/pandas.xlsx
@@ -4,21 +4,22 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="basics" sheetId="2" r:id="rId2"/>
     <sheet name="numpy" sheetId="3" r:id="rId3"/>
     <sheet name="CheetSheet" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
+    <sheet name="cheet_sheet" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="1059">
   <si>
     <t>Series</t>
   </si>
@@ -23177,18 +23178,1714 @@
   </si>
   <si>
     <t>aggregation</t>
+  </si>
+  <si>
+    <t>find missing cells in Column_B from Column_A</t>
+  </si>
+  <si>
+    <t>from pathlib import Path</t>
+  </si>
+  <si>
+    <t>excel_path = Path(r"C:\Users\user\Desktop\work_folder\excel_tricks\missing_file.xlsx")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ~df["Column_A"].isin(df["Column_B"]),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Column_A"</t>
+  </si>
+  <si>
+    <t>]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Output: </t>
+  </si>
+  <si>
+    <t># The number 3000072870 is in Column_A but missing in Column_B and is located at 38335 row in Column_A</t>
+  </si>
+  <si>
+    <t>Excel row: 38335, Value: 3000072870</t>
+  </si>
+  <si>
+    <t>Column_A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(excel_path, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usecols</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="A,B", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>header</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=None)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.columns = ["Column_A", "Column_B"]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>missing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.loc[</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>missing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;class 'pandas.core.series.Series'&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;class 'zip'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;zip object at 0x000000000B84F080&gt;</t>
+  </si>
+  <si>
+    <t>print(missing.items())</t>
+  </si>
+  <si>
+    <t>print(type(missing.items()))</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>idx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, value in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>missing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>items</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>():</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Get Column_A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["Column_A"]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    ~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"]),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>returns:</t>
+  </si>
+  <si>
+    <t>0    100</t>
+  </si>
+  <si>
+    <t>1    300</t>
+  </si>
+  <si>
+    <t>2    500</t>
+  </si>
+  <si>
+    <t>3    900</t>
+  </si>
+  <si>
+    <t>Name: Column_A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Check if each value exists in Column_B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() means:</t>
+    </r>
+  </si>
+  <si>
+    <t>"Is each value in this Series contained in another list/Series?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Column_A    Column_B</t>
+  </si>
+  <si>
+    <t>0      100        200</t>
+  </si>
+  <si>
+    <t>1      300        300</t>
+  </si>
+  <si>
+    <t>2      500        700</t>
+  </si>
+  <si>
+    <t>3      900        500</t>
+  </si>
+  <si>
+    <t>example dataframe</t>
+  </si>
+  <si>
+    <t>0    False</t>
+  </si>
+  <si>
+    <t>1     True</t>
+  </si>
+  <si>
+    <t>2     True</t>
+  </si>
+  <si>
+    <t>3    False</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This is called a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>boolean mask</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Reverse the result with ~</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"])</t>
+    </r>
+  </si>
+  <si>
+    <t>Before:</t>
+  </si>
+  <si>
+    <t>After:</t>
+  </si>
+  <si>
+    <t>0     True</t>
+  </si>
+  <si>
+    <t>1    False</t>
+  </si>
+  <si>
+    <t>2    False</t>
+  </si>
+  <si>
+    <t>3     True</t>
+  </si>
+  <si>
+    <t>Meaning:</t>
+  </si>
+  <si>
+    <t>Keep rows where Column_A is NOT found in Column_B</t>
+  </si>
+  <si>
+    <t>So .loc receives:</t>
+  </si>
+  <si>
+    <t>df.loc[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    [True, False, False, True],</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ...</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Part 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Selecting the column</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>means:</t>
+  </si>
+  <si>
+    <t>After filtering the rows, return only this column - Column_A</t>
+  </si>
+  <si>
+    <t>So:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    row_condition,</t>
+  </si>
+  <si>
+    <r>
+      <t>df.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>loc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+  </si>
+  <si>
+    <t>is equivalent to:</t>
+  </si>
+  <si>
+    <t>Give me Column_A values from rows where the condition is True.</t>
+  </si>
+  <si>
+    <t>38334    3000072870</t>
+  </si>
+  <si>
+    <t>38374    3000072910</t>
+  </si>
+  <si>
+    <t>38422    3000072958</t>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>missing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Excel row: 38375, Value: 3000072910</t>
+  </si>
+  <si>
+    <t>Excel row: 38423, Value: 3000072958</t>
+  </si>
+  <si>
+    <t>Exploanation:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    print(f"Excel row: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>idx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + 1}, Value: {value}")</t>
+    </r>
+  </si>
+  <si>
+    <t>find_missing.py</t>
+  </si>
+  <si>
+    <t>pivot.py</t>
+  </si>
+  <si>
+    <t>excel_path = Path(r"C:\Users\user\Desktop\work_folder\excel_tricks\pivot.xlsx")</t>
+  </si>
+  <si>
+    <t>iterrows() дава всеки ред от df като серия</t>
+  </si>
+  <si>
+    <t>Column_A    2CDS251001R0104</t>
+  </si>
+  <si>
+    <t>Column_B                  3</t>
+  </si>
+  <si>
+    <t>2CDS251001R0104</t>
+  </si>
+  <si>
+    <t>Column_B</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    print(f"{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>['</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>']};{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>['</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>']}")</t>
+    </r>
+  </si>
+  <si>
+    <t>2CDS251001R0104;3</t>
+  </si>
+  <si>
+    <t>2CDS251001R0164;14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iterrows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>():</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">result_df </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>agg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>({"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": "sum"})</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    # print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    # print(type(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = ред от df, като серия</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">i </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= индекса на всeки един ред от df. Започва от 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(excel_path, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usecols</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="A,B", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>header</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=None)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.columns = ["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"]</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="57">
+  <fonts count="61">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23628,6 +25325,23 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF179A77"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -23824,10 +25538,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -23837,158 +25551,158 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -24001,18 +25715,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27253,6 +28974,58 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>36786</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>26276</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>509752</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>27864</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6742386" y="18603310"/>
+          <a:ext cx="1082566" cy="1588"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -38386,7 +40159,7 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="144" t="s">
+      <c r="E16" s="151" t="s">
         <v>842</v>
       </c>
       <c r="F16" s="7"/>
@@ -38449,4 +40222,655 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N110"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="23" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="B2" s="149" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="146"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="B4" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5" s="6" t="s">
+        <v>966</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9" s="147" t="s">
+        <v>975</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10" s="147" t="s">
+        <v>976</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" s="147" t="s">
+        <v>977</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="G12" s="148" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13" s="6" t="s">
+        <v>968</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="G14" t="s">
+        <v>982</v>
+      </c>
+      <c r="J14" t="s">
+        <v>981</v>
+      </c>
+      <c r="N14" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="8"/>
+      <c r="G15" t="s">
+        <v>979</v>
+      </c>
+      <c r="J15" t="s">
+        <v>980</v>
+      </c>
+      <c r="N15" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
+      <c r="N16" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8"/>
+      <c r="G17" t="s">
+        <v>971</v>
+      </c>
+      <c r="N17" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="11"/>
+      <c r="G18" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="G19" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="G20" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="G22" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="23" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="148" t="s">
+        <v>977</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="7" t="s">
+        <v>986</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="7" t="s">
+        <v>987</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="7"/>
+      <c r="G30" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="7"/>
+      <c r="G31" s="9" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="7"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="7"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="149" t="s">
+        <v>984</v>
+      </c>
+      <c r="G34" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="C35" s="149" t="s">
+        <v>985</v>
+      </c>
+      <c r="H35" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="H36" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="H37" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="H38" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="H39" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="149" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="C42" s="150" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="C44" s="149" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="D45" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="D47" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="D48" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="D49" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="D50" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" s="149" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="C55" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="C56" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="C57" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D57" s="150" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="C58" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="C59" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="C61" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="D62" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="C63" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="D64" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="D65" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="D66" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="D67" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8">
+      <c r="B69" s="149" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8">
+      <c r="C71" s="148" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8">
+      <c r="C72" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8">
+      <c r="C73" s="7" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="C74" s="7" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
+      <c r="C76" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="D77" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="C79" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="D80" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="D81" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="D82" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="D83" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="23" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="B87" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="5"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="B88" s="6" t="s">
+        <v>966</v>
+      </c>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="8"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="B89" s="6"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="8"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="B90" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="8"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="B91" s="6"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="8"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="B92" s="152" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="8"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="B93" s="152" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="8"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="B94" s="6"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="8"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="B95" s="6"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="8"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="B96" s="152" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="8"/>
+    </row>
+    <row r="97" spans="2:10">
+      <c r="B97" s="6"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="8"/>
+    </row>
+    <row r="98" spans="2:10">
+      <c r="B98" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="8"/>
+      <c r="G98" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10">
+      <c r="B99" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C99" s="10"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="11"/>
+      <c r="G99" s="149" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10">
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="G100" s="149" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10">
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="G101" s="2" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10">
+      <c r="G102" s="2" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10">
+      <c r="B103" s="23" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10">
+      <c r="B105" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I105" t="s">
+        <v>974</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10">
+      <c r="D106" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I106" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10">
+      <c r="D107" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10">
+      <c r="B109" s="7" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10">
+      <c r="D110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/pandas.xlsx
+++ b/pandas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="1101">
   <si>
     <t>Series</t>
   </si>
@@ -23207,9 +23207,6 @@
     <t>Excel row: 38335, Value: 3000072870</t>
   </si>
   <si>
-    <t>Column_A</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -24263,19 +24260,996 @@
     <t>excel_path = Path(r"C:\Users\user\Desktop\work_folder\excel_tricks\pivot.xlsx")</t>
   </si>
   <si>
-    <t>iterrows() дава всеки ред от df като серия</t>
-  </si>
-  <si>
-    <t>Column_A    2CDS251001R0104</t>
-  </si>
-  <si>
-    <t>Column_B                  3</t>
-  </si>
-  <si>
-    <t>2CDS251001R0104</t>
-  </si>
-  <si>
-    <t>Column_B</t>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iterrows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>():</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = ред от df, като серия</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">i </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= индекса на всeки един ред от df. Започва от 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(index, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">where </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is a Series, not the actual value</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">() uses </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True by default</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(excel_path, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usecols</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="B,C,J", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>header</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=None)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.columns = ["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>notna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    })</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>agg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>({</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": "first",</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": "sum",</t>
+    </r>
+  </si>
+  <si>
+    <t>print("________________________\n")</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>['</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>']</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>['</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>']).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>replace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('.', ',')  # quantity is str</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>['</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>']).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
   </si>
   <si>
     <r>
@@ -24284,6 +25258,309 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>};{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>};{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import pandas as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pd</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">from pathlib import </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Path</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iterrows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() returns:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iterrows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() дава всеки ред от df като серия</t>
+    </r>
+  </si>
+  <si>
+    <t>Article                                          194691</t>
+  </si>
+  <si>
+    <t>Quantity                                          603.0</t>
+  </si>
+  <si>
+    <t>Description    Дефектнотокова защита EATON HNC-40/2/003</t>
+  </si>
+  <si>
+    <t>Article</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>603.0</t>
+  </si>
+  <si>
+    <t>Дефектнотокова защита EATON HNC-40/2/003</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If you use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True column "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" becomes index for the new dataframe - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_df</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>by using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" will be normal column in the new df - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_df</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color rgb="FFC00000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -24300,6 +25577,300 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(type(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t>създаваме df използвайки само колоните "B,C,J"</t>
+  </si>
+  <si>
+    <t>задаваме нови имена на колоните</t>
+  </si>
+  <si>
+    <t>филтрираме вече създадената df като оставаме само редовете където в колона "Quantity" има стойност</t>
+  </si>
+  <si>
+    <r>
+      <t>Казваме - остави само уникалните редове в колона "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">създаваме нова </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> която ще бъде пивот таблица(df)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">избираме </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False за да си оставим колона "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" да бъде обикновенна колона а не да стане index kolona</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>за всички еднакви редове на "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" остави 1 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>и в колона "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" сложи стойността на първия срещнат</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>а в колона "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" сумирай стойностите им</t>
+    </r>
+  </si>
+  <si>
+    <t>194691;Дефектнотокова защита EATON HNC-40/2/003;603,0</t>
+  </si>
+  <si>
+    <t>194829;Автоматичен прекъсвач EATON HN-C10/1;601,0</t>
+  </si>
+  <si>
+    <t>194831;Автоматичен прекъсвач EATON HN-C16/1;3878,0</t>
+  </si>
+  <si>
+    <t>Output:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">За всеки </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>индекс</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ред(194691, Деф.., 603,0) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>от таблицата</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>['</t>
     </r>
     <r>
@@ -24311,18 +25882,20 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Column_A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>']};{</t>
-    </r>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'] = 194691</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -24353,50 +25926,20 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Column_B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>']}")</t>
-    </r>
-  </si>
-  <si>
-    <t>2CDS251001R0104;3</t>
-  </si>
-  <si>
-    <t>2CDS251001R0164;14</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF002060"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'] = Дефектнотокова защита EATON HNC-40/2/003</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -24416,8 +25959,118 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> in </t>
-    </r>
+      <t>[''</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>''] = 603,0</t>
+    </r>
+  </si>
+  <si>
+    <t>Ако искаме да добавим нова колона в която да е броя на агрегираните редове, просто заменяме:</t>
+  </si>
+  <si>
+    <t>с:</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Description=("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "first"),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Quantity=("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "sum"),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Count=("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "count")</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -24437,7 +26090,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.</t>
+      <t xml:space="preserve"> = df.</t>
     </r>
     <r>
       <rPr>
@@ -24448,61 +26101,59 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>iterrows</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>():</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">result_df </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>df</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
+      <t>groupby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Article</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False).</t>
     </r>
     <r>
       <rPr>
@@ -24513,69 +26164,6 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>groupby</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>("</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF179A77"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Column_A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">", </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>as_index</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=False).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA47A20"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>agg</t>
     </r>
     <r>
@@ -24586,290 +26174,31 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>({"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF179A77"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Column_B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>": "sum"})</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">    # print(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>row</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">    # print(type(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>row</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>row</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = ред от df, като серия</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF002060"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">i </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>= индекса на всeки един ред от df. Започва от 0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>df</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = pd.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA47A20"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>read_excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">(excel_path, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>usecols</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">="A,B", </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>header</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=None)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>df</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.columns = ["</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF179A77"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Column_A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>", "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF179A77"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Column_B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"]</t>
-    </r>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <t>Named Aggregation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="61">
+  <fonts count="62">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -25538,10 +26867,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -25551,158 +26880,158 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -25715,25 +27044,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28978,16 +30310,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>36786</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>26276</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>310055</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>110359</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>509752</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>27864</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>173421</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>111947</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -28996,7 +30328,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6742386" y="18603310"/>
+          <a:off x="5186855" y="21814221"/>
           <a:ext cx="1082566" cy="1588"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -40226,12 +41558,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N110"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="23" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -40280,7 +41612,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="B9" s="147" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -40288,7 +41620,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="B10" s="147" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -40302,13 +41634,13 @@
     </row>
     <row r="12" spans="1:14">
       <c r="B12" s="147" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
       <c r="G12" s="148" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -40327,13 +41659,13 @@
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
       <c r="G14" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="J14" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="N14" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -40344,13 +41676,13 @@
       <c r="D15" s="7"/>
       <c r="E15" s="8"/>
       <c r="G15" t="s">
+        <v>978</v>
+      </c>
+      <c r="J15" t="s">
         <v>979</v>
       </c>
-      <c r="J15" t="s">
-        <v>980</v>
-      </c>
       <c r="N15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -40359,12 +41691,12 @@
       <c r="D16" s="7"/>
       <c r="E16" s="8"/>
       <c r="N16" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="17" spans="2:14">
       <c r="B17" s="6" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -40373,12 +41705,12 @@
         <v>971</v>
       </c>
       <c r="N17" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="18" spans="2:14">
       <c r="B18" s="9" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -40389,12 +41721,12 @@
     </row>
     <row r="19" spans="2:14">
       <c r="G19" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="20" spans="2:14">
       <c r="G20" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -40404,33 +41736,33 @@
     </row>
     <row r="24" spans="2:14">
       <c r="B24" s="23" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="26" spans="2:14">
       <c r="B26" s="148" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G26" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="27" spans="2:14">
       <c r="B27" s="7" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="2:14">
       <c r="B28" s="7" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="8"/>
@@ -40440,7 +41772,7 @@
         <v>970</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="8"/>
@@ -40448,7 +41780,7 @@
     <row r="30" spans="2:14">
       <c r="B30" s="7"/>
       <c r="G30" s="6" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="8"/>
@@ -40456,7 +41788,7 @@
     <row r="31" spans="2:14">
       <c r="B31" s="7"/>
       <c r="G31" s="9" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="11"/>
@@ -40469,159 +41801,159 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="149" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G34" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="C35" s="149" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H35" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="H36" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="H37" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="H38" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="H39" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="149" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="C42" s="150" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="C44" s="149" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="D45" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="D47" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="D48" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="D49" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="D50" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F50" t="s">
         <v>1007</v>
-      </c>
-      <c r="F50" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="149" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="C55" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H55" t="s">
         <v>1011</v>
-      </c>
-      <c r="H55" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="C56" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H56" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="C57" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D57" s="150" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H57" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="C58" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H58" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="59" spans="2:8">
       <c r="C59" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H59" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="C61" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="D62" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="C63" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="D64" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="65" spans="2:8">
       <c r="D65" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="D66" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -40631,22 +41963,22 @@
     </row>
     <row r="69" spans="2:8">
       <c r="B69" s="149" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="C71" s="148" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="C72" s="7" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="C73" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -40656,217 +41988,524 @@
     </row>
     <row r="76" spans="2:8">
       <c r="C76" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="77" spans="2:8">
       <c r="D77" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="79" spans="2:8">
       <c r="C79" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G79" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="80" spans="2:8">
       <c r="D80" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H80" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="D81" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="D82" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="D83" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:9">
       <c r="A85" s="23" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="B87" s="3" t="s">
-        <v>217</v>
+        <v>1060</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:9">
       <c r="B88" s="6" t="s">
-        <v>966</v>
+        <v>1061</v>
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="8"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:9">
       <c r="B89" s="6"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:9">
       <c r="B90" s="6" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="8"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:9">
       <c r="B91" s="6"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="8"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:9">
       <c r="B92" s="152" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="8"/>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="B93" s="152" t="s">
-        <v>1058</v>
+      <c r="I92" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="B93" s="154" t="s">
+        <v>1049</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="8"/>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="I93" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="B94" s="6"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="8"/>
     </row>
-    <row r="95" spans="1:5">
-      <c r="B95" s="6"/>
+    <row r="95" spans="1:9">
+      <c r="B95" s="152" t="s">
+        <v>1050</v>
+      </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="8"/>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="B96" s="152" t="s">
-        <v>1052</v>
-      </c>
+      <c r="I95" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="B96" s="152"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="8"/>
     </row>
     <row r="97" spans="2:10">
-      <c r="B97" s="6"/>
+      <c r="B97" s="152" t="s">
+        <v>1052</v>
+      </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="8"/>
+      <c r="I97" t="s">
+        <v>1080</v>
+      </c>
     </row>
     <row r="98" spans="2:10">
-      <c r="B98" s="6" t="s">
-        <v>1051</v>
+      <c r="B98" s="152" t="s">
+        <v>1053</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="8"/>
-      <c r="G98" t="s">
-        <v>1043</v>
+      <c r="I98" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="99" spans="2:10">
-      <c r="B99" s="9" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="11"/>
-      <c r="G99" s="149" t="s">
-        <v>1056</v>
+      <c r="B99" s="152" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="8"/>
+      <c r="I99" t="s">
+        <v>1079</v>
       </c>
     </row>
     <row r="100" spans="2:10">
-      <c r="B100" s="7"/>
+      <c r="B100" s="152" t="s">
+        <v>1051</v>
+      </c>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="G100" s="149" t="s">
-        <v>1055</v>
+      <c r="E100" s="8"/>
+      <c r="I100" t="s">
+        <v>1082</v>
       </c>
     </row>
     <row r="101" spans="2:10">
-      <c r="B101" s="7"/>
+      <c r="B101" s="152"/>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="G101" s="2" t="s">
-        <v>1049</v>
+      <c r="E101" s="8"/>
+      <c r="J101" t="s">
+        <v>1083</v>
       </c>
     </row>
     <row r="102" spans="2:10">
-      <c r="G102" s="2" t="s">
-        <v>1050</v>
+      <c r="B102" s="152" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="8"/>
+      <c r="J102" t="s">
+        <v>1084</v>
       </c>
     </row>
     <row r="103" spans="2:10">
-      <c r="B103" s="23" t="s">
-        <v>1038</v>
-      </c>
+      <c r="B103" s="152"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="8"/>
+    </row>
+    <row r="104" spans="2:10">
+      <c r="B104" s="6"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="8"/>
     </row>
     <row r="105" spans="2:10">
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="8"/>
+      <c r="I105" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10">
+      <c r="B106" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="8"/>
+      <c r="J106" s="153" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10">
+      <c r="B107" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="8"/>
+      <c r="J107" s="153" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10">
+      <c r="B108" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="8"/>
+      <c r="J108" s="153" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10">
+      <c r="B109" s="6"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="8"/>
+    </row>
+    <row r="110" spans="2:10">
+      <c r="B110" s="9" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C110" s="10"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="11"/>
+    </row>
+    <row r="111" spans="2:10">
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+    </row>
+    <row r="112" spans="2:10">
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="I112" s="23" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="113" spans="2:14">
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="I113" s="2" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="114" spans="2:14">
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="I114" s="2" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="115" spans="2:14">
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
+      <c r="I115" s="2" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="116" spans="2:14">
+      <c r="B116" s="7"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
+    </row>
+    <row r="117" spans="2:14">
+      <c r="B117" s="23" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="119" spans="2:14">
+      <c r="B119" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="120" spans="2:14">
+      <c r="D120" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L120" s="129" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M120" s="129" t="s">
+        <v>1068</v>
+      </c>
+      <c r="N120" s="129" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="121" spans="2:14">
+      <c r="D121" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L121" s="22">
+        <v>194691</v>
+      </c>
+      <c r="M121" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="N121" s="22" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="122" spans="2:14">
+      <c r="D122" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="124" spans="2:14">
+      <c r="B124" s="7" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="125" spans="2:14">
+      <c r="D125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="2:14">
+      <c r="B128" s="153" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3">
+      <c r="C129" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3">
+      <c r="C130" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3">
+      <c r="C132" s="153" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="C133" s="149" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3">
+      <c r="C134" s="149" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3">
+      <c r="B136" s="155" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3">
+      <c r="B137" s="155" t="s">
         <v>1053</v>
       </c>
-      <c r="D105" t="s">
-        <v>1044</v>
-      </c>
-      <c r="I105" t="s">
-        <v>974</v>
-      </c>
-      <c r="J105" t="s">
+    </row>
+    <row r="138" spans="2:3">
+      <c r="B138" s="155" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3">
+      <c r="B139" s="155" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3">
+      <c r="C141" s="153" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="106" spans="2:10">
-      <c r="D106" t="s">
-        <v>1045</v>
-      </c>
-      <c r="I106" t="s">
-        <v>1046</v>
-      </c>
-      <c r="J106">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10">
-      <c r="D107" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="109" spans="2:10">
-      <c r="B109" s="7" t="s">
+    <row r="142" spans="2:3">
+      <c r="C142" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3">
+      <c r="C143" s="153" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="23" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="23"/>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="B147" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="B148" s="7"/>
+      <c r="C148" s="155" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D148" s="7"/>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="B149" s="7"/>
+      <c r="C149" s="155" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D149" s="7"/>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="B150" s="7"/>
+      <c r="C150" s="155" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="110" spans="2:10">
-      <c r="D110" t="s">
-        <v>11</v>
-      </c>
+      <c r="D150" s="7"/>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="B151" s="7"/>
+      <c r="C151" s="155" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D151" s="7"/>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="B152" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="B153" s="7"/>
+      <c r="C153" s="155" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D153" s="7"/>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="B154" s="7"/>
+      <c r="C154" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D154" s="7"/>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="B155" s="7"/>
+      <c r="C155" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D155" s="7"/>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="B156" s="7"/>
+      <c r="C156" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D156" s="7"/>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="B157" s="7"/>
+      <c r="C157" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D157" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pandas.xlsx
+++ b/pandas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="CheetSheet" sheetId="4" r:id="rId4"/>
     <sheet name="cheet_sheet" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="1274">
   <si>
     <t>Series</t>
   </si>
@@ -26179,18 +26180,3252 @@
   </si>
   <si>
     <t>Named Aggregation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      A</t>
+  </si>
+  <si>
+    <t>0     1</t>
+  </si>
+  <si>
+    <t>1     2</t>
+  </si>
+  <si>
+    <t>4  None</t>
+  </si>
+  <si>
+    <t>2     a</t>
+  </si>
+  <si>
+    <t>3     4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = pd.DataFrame({</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>2  &lt;NA&gt;</t>
+  </si>
+  <si>
+    <t>3  &lt;NA&gt;</t>
+  </si>
+  <si>
+    <t>4  &lt;NA&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": ["1", "2", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>xyz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", None]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to_numeric</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">["A"], </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>errors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="coerce").</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>astype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("Int64")</t>
+    </r>
+  </si>
+  <si>
+    <t>"Int64" keeps the column as integers while allowing missing values</t>
+  </si>
+  <si>
+    <r>
+      <t>Тук "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>а</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" и "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>xyz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" стават &lt;NA&gt; </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>errors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="coerce" turns invalid values into NaN</t>
+    </r>
+  </si>
+  <si>
+    <t>двете заедно позволяват "a", "xyz" да се превърнат в &lt;NA&gt; без програмата да се счупи</t>
+  </si>
+  <si>
+    <t>опитай се да превърнеш всеки ред в тази колона в iномер(float) и ако не успееш го запиши като &lt;NA&gt; празна клетка</t>
+  </si>
+  <si>
+    <t>превърни всички клетки в тази колона в int като ако са празни не хвърляй грешка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     A</t>
+  </si>
+  <si>
+    <t>0  1.0</t>
+  </si>
+  <si>
+    <t>1  2.0</t>
+  </si>
+  <si>
+    <t>2  NaN</t>
+  </si>
+  <si>
+    <t>3  NaN</t>
+  </si>
+  <si>
+    <t>4  NaN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ако</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> е без .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>astype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("Int64")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">защото </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to_numeric</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() превръща str -&gt; float</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ако</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> е без </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>errors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">="coerce" </t>
+    </r>
+  </si>
+  <si>
+    <t>ValueError: Unable to parse string "a" at position 2</t>
+  </si>
+  <si>
+    <t>дава грешка, защото не може да parse-не "а" -&gt; float</t>
+  </si>
+  <si>
+    <t>print(invalid_s)</t>
+  </si>
+  <si>
+    <t>3    xyz</t>
+  </si>
+  <si>
+    <t>Name: A, dtype: object</t>
+  </si>
+  <si>
+    <t>2       a</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Извади</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> невалидните клетки "a", "xyz"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": ["1", "2", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>xyz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", None]</t>
+    </r>
+  </si>
+  <si>
+    <t>0    1.0</t>
+  </si>
+  <si>
+    <t>1    2.0</t>
+  </si>
+  <si>
+    <t>2    NaN</t>
+  </si>
+  <si>
+    <t>3    NaN</t>
+  </si>
+  <si>
+    <t>4    NaN</t>
+  </si>
+  <si>
+    <t>Name: A, dtype: float64</t>
+  </si>
+  <si>
+    <t>4    False</t>
+  </si>
+  <si>
+    <t>Name: A, dtype: bool</t>
+  </si>
+  <si>
+    <r>
+      <t>print(df["A"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>notna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>())</t>
+    </r>
+  </si>
+  <si>
+    <t>4     True</t>
+  </si>
+  <si>
+    <r>
+      <t>print(df["A"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>())</t>
+    </r>
+  </si>
+  <si>
+    <t>празна ли е клетката</t>
+  </si>
+  <si>
+    <t>не е ли празна</t>
+  </si>
+  <si>
+    <t>3     xyz</t>
+  </si>
+  <si>
+    <t>4    None</t>
+  </si>
+  <si>
+    <t>резултат</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"][</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>converted_serie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()])</t>
+    </r>
+  </si>
+  <si>
+    <t>df["A"]</t>
+  </si>
+  <si>
+    <t>2        a</t>
+  </si>
+  <si>
+    <t>0        1</t>
+  </si>
+  <si>
+    <t>1        2</t>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>converted_serie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["A"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>notna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>оригинална df</t>
+  </si>
+  <si>
+    <t>bool mask 1</t>
+  </si>
+  <si>
+    <t>result 1</t>
+  </si>
+  <si>
+    <t>bool mask 2</t>
+  </si>
+  <si>
+    <t>result 2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>converted_s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to_numeric</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"], </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>errors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="coerce")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>invalid_s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"][converted_s.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">() &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>notna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": ["1", "2", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>xyz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", None]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>invalid_s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"][converted_s.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">() &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>notna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>converted_s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()]</t>
+    </r>
+  </si>
+  <si>
+    <t>df["A"][converted_s.isna()</t>
+  </si>
+  <si>
+    <t>df["A"][converted_s.isna() &amp; df["A"].notna()]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Превърни</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> числата от str -&gt; int, с останалите които не могат ги направи на празни клетни &lt;NA&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Превърни</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> числата от str -&gt; int, с останалите които не могат ги направи на 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fillna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>astype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(int)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": ["1", "2", "a", "xyz", None]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to_numeric</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"], </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>errors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="coerce")</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   A</t>
+  </si>
+  <si>
+    <t>1  2</t>
+  </si>
+  <si>
+    <t>2  0</t>
+  </si>
+  <si>
+    <t>3  0</t>
+  </si>
+  <si>
+    <t>4  0</t>
+  </si>
+  <si>
+    <t>защо тук слагаме скобите</t>
+  </si>
+  <si>
+    <t>3   xyz</t>
+  </si>
+  <si>
+    <t>Как да провериме колко реда има в DF</t>
+  </si>
+  <si>
+    <t>(5, 1)</t>
+  </si>
+  <si>
+    <t>5 реда, 1 колона</t>
+  </si>
+  <si>
+    <t>5 реда</t>
+  </si>
+  <si>
+    <r>
+      <t>print(len(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.shape)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.shape[0])</t>
+    </r>
+  </si>
+  <si>
+    <t>print(df.index.size)</t>
+  </si>
+  <si>
+    <t>Read only what you need</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>excel_path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usecols</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=["Name", "Age", "Salary"],</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nrows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1000,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dtype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>={"Age": "Int64"}</t>
+    </r>
+  </si>
+  <si>
+    <t>използвай само тези колони</t>
+  </si>
+  <si>
+    <t>използвай само тези редове</t>
+  </si>
+  <si>
+    <t>парсни колона "Age" към int</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read_excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <t>Set data types as early as possible</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to_numeric</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"], </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>errors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>="coerce")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fillna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>astype</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(int)</t>
+    </r>
+  </si>
+  <si>
+    <t>Use vectorized operations</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adults</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 30]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Names</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": ["Sikato", "Boce", "Slavi", None],</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": [34, 33, 17, 0]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adults</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    Names  Age</t>
+  </si>
+  <si>
+    <t>0  Sikato   34</t>
+  </si>
+  <si>
+    <t>1    Boce   33</t>
+  </si>
+  <si>
+    <t>2   Slavi   17</t>
+  </si>
+  <si>
+    <t>3    None    0</t>
+  </si>
+  <si>
+    <t>adults</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">тук </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adults</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> е нова </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> която съдържа само филтрираните редове</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Adult</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 30</t>
+    </r>
+  </si>
+  <si>
+    <t>0  Sikato   34   True</t>
+  </si>
+  <si>
+    <t>1    Boce   33   True</t>
+  </si>
+  <si>
+    <t>2   Slavi   17  False</t>
+  </si>
+  <si>
+    <t>3    None    0  False</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Names  Age  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Adult</t>
+    </r>
+  </si>
+  <si>
+    <t>Добавяяме нова колона с bool-ва стойност</t>
+  </si>
+  <si>
+    <t>df - after</t>
+  </si>
+  <si>
+    <t>df - before</t>
+  </si>
+  <si>
+    <t>df = df[df["Age"] &gt; 30]  така е същото но се променя оригиналната df</t>
+  </si>
+  <si>
+    <t>Преименуване на колона с bool-ви стойности</t>
+  </si>
+  <si>
+    <r>
+      <t>df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Names</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   Names  Age</t>
+  </si>
+  <si>
+    <t>0   True   34</t>
+  </si>
+  <si>
+    <t>1   True   33</t>
+  </si>
+  <si>
+    <t>2  False   17</t>
+  </si>
+  <si>
+    <t>3  False    0</t>
+  </si>
+  <si>
+    <t>before</t>
+  </si>
+  <si>
+    <t>after</t>
+  </si>
+  <si>
+    <t>Use column operations</t>
+  </si>
+  <si>
+    <r>
+      <t>df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] * 1.2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    Names   Age</t>
+  </si>
+  <si>
+    <t>0  Sikato  40.8</t>
+  </si>
+  <si>
+    <t>1    Boce  39.6</t>
+  </si>
+  <si>
+    <t>2   Slavi  20.4</t>
+  </si>
+  <si>
+    <t>3    None   0.0</t>
+  </si>
+  <si>
+    <t>Filter with boolean indexing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 30]</t>
+    </r>
+  </si>
+  <si>
+    <t>Typical pandas workflow</t>
+  </si>
+  <si>
+    <t># Read</t>
+  </si>
+  <si>
+    <t># Clean</t>
+  </si>
+  <si>
+    <t># Filter</t>
+  </si>
+  <si>
+    <t># Add new column</t>
+  </si>
+  <si>
+    <t># Sort</t>
+  </si>
+  <si>
+    <t># Save</t>
+  </si>
+  <si>
+    <t>df.to_excel("output.xlsx", index=False)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = pd.read_excel("input.xlsx")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    pd.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to_numeric</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"], errors="coerce")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df = df[df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 0]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Total</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] * df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df = df.sort_values("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Total</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", ascending=False)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df.loc[df["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] &gt; 18, "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Adult</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"] = True</t>
+    </r>
+  </si>
+  <si>
+    <t>0  Sikato   34  True</t>
+  </si>
+  <si>
+    <t>1    Boce   33  True</t>
+  </si>
+  <si>
+    <t>2   Slavi   17   NaN</t>
+  </si>
+  <si>
+    <t>3    None    0   NaN</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Names  Age </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Adult</t>
+    </r>
+  </si>
+  <si>
+    <t>Добавяяме нова колона с bool-ва стойност + &lt;Na&gt; вместо False</t>
+  </si>
+  <si>
+    <t>Sort values</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": [34, 37, 17, 0]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = df.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sort_values</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ascending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=False)</t>
+    </r>
+  </si>
+  <si>
+    <t>1    Boce   37</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="62">
+  <fonts count="65">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -26671,6 +29906,13 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -26867,10 +30109,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -26880,158 +30122,158 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -27044,28 +30286,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27076,9 +30333,9 @@
     <mruColors>
       <color rgb="FF179A77"/>
       <color rgb="FFA47A20"/>
+      <color rgb="FFA626A4"/>
       <color rgb="FF64AF8C"/>
       <color rgb="FFDA7BB9"/>
-      <color rgb="FFA626A4"/>
       <color rgb="FFFF33CC"/>
       <color rgb="FF1E7D6A"/>
       <color rgb="FF005F6A"/>
@@ -30358,6 +33615,152 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>242891</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>561974</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3900491" y="5743576"/>
+          <a:ext cx="928683" cy="790574"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>519116</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>528638</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2957516" y="9796463"/>
+          <a:ext cx="2447922" cy="557213"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>604839</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>557214</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Arrow Connector 4"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="1214439" y="15497174"/>
+          <a:ext cx="3000375" cy="347663"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -42512,4 +45915,2176 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L257"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="168" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="I2" s="158" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5"/>
+      <c r="I3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="I4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" s="157" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
+      <c r="I5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="I6" s="156" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="I7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="I8" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="157" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="2"/>
+      <c r="C14" s="159" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="2"/>
+      <c r="C15" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="C17" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="B19" s="159" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F19" s="159" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="C20" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="C21" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="C22" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="C23" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="C24" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="C25" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="C27" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="159" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5"/>
+      <c r="I31" s="45" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="8"/>
+      <c r="I32" s="19" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="157" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="8"/>
+      <c r="I33" s="19" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8"/>
+      <c r="I34" s="19" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="8"/>
+      <c r="I35" s="19" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="8"/>
+      <c r="I36" s="161" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="167" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="8"/>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="167" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
+      <c r="I38" s="160" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" s="6"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="8"/>
+      <c r="I39" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="9" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="11"/>
+      <c r="I40" s="2" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="162" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="7" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="82" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="C49" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="C50" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="C51" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="C52" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="C53" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="C54" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="J55" s="45" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="159" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J56" s="19" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="159"/>
+      <c r="J57" s="19" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="C58" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1159</v>
+      </c>
+      <c r="J58" s="19" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="C59" s="45" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H59" s="46" t="s">
+        <v>1153</v>
+      </c>
+      <c r="J59" s="19" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
+      <c r="C60" s="19" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H60" s="19"/>
+      <c r="J60" s="161" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="C61" s="164" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E61" s="163" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H61" s="164" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10">
+      <c r="C62" s="19" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E62" s="163" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10">
+      <c r="C63" s="19" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E63" s="163" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10">
+      <c r="C64" s="161" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="B67" s="168" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="C69" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1163</v>
+      </c>
+      <c r="J69" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="C71" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I71" t="s">
+        <v>76</v>
+      </c>
+      <c r="J71" s="159" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L71" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="C72" s="45" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E72" s="45" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H72" s="165"/>
+      <c r="J72" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="C73" s="19" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H73" s="7"/>
+      <c r="J73" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L73" s="165"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="C74" s="164" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E74" s="163" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H74" s="166" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J74" t="s">
+        <v>1005</v>
+      </c>
+      <c r="L74" s="7"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="C75" s="19" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E75" s="163" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H75" s="19" t="s">
+        <v>1151</v>
+      </c>
+      <c r="J75" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L75" s="166" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="C76" s="19" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E76" s="163" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H76" s="19" t="s">
+        <v>1152</v>
+      </c>
+      <c r="J76" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L76" s="19" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="C77" s="161" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H77" s="20" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J77" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L77" s="20" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="168" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="B82" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="5"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="B83" s="6"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="8"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="B84" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="8"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="B85" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="8"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="B86" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="8"/>
+      <c r="H86" s="78" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="B87" s="6"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="8"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="B88" s="169" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="8"/>
+      <c r="J88" s="158" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="B89" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="8"/>
+      <c r="H89" s="45" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J89" s="70" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="B90" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="8"/>
+      <c r="H90" s="19" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J90" s="71" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="B91" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="8"/>
+      <c r="H91" s="19" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J91" s="71" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="B92" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="8"/>
+      <c r="H92" s="164" t="s">
+        <v>1105</v>
+      </c>
+      <c r="J92" s="71" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="B93" s="6"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="8"/>
+      <c r="H93" s="19" t="s">
+        <v>1186</v>
+      </c>
+      <c r="J93" s="71" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="B94" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C94" s="10"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="11"/>
+      <c r="H94" s="20" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J94" s="100" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="168"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="23" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="B98" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="5"/>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="B99" s="6"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="8"/>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="B100" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="8"/>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="B101" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="8"/>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="B102" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="8"/>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="B103" s="6"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="8"/>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="B104" s="6" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="8"/>
+      <c r="H104" s="2">
+        <v>5</v>
+      </c>
+      <c r="I104" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="B105" s="6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="8"/>
+      <c r="H105" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="B106" s="6" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="8"/>
+      <c r="H106" s="2">
+        <v>5</v>
+      </c>
+      <c r="I106" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="B107" s="6" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="8"/>
+      <c r="H107" s="2">
+        <v>5</v>
+      </c>
+      <c r="I107" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="B108" s="6"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="8"/>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="B109" s="9"/>
+      <c r="C109" s="10"/>
+      <c r="D109" s="10"/>
+      <c r="E109" s="10"/>
+      <c r="F109" s="11"/>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="23" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="B113" s="170" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="5"/>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="B114" s="6" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="8"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="B115" s="6" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="8"/>
+      <c r="G115" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="B116" s="6" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="8"/>
+      <c r="G116" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="B117" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="8"/>
+      <c r="G117" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="B118" s="9" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C118" s="10"/>
+      <c r="D118" s="10"/>
+      <c r="E118" s="11"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="23" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="B122" s="170" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="5"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="B123" s="6" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="8"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="B124" s="6" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="8"/>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="B125" s="6" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="8"/>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="B126" s="9" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C126" s="10"/>
+      <c r="D126" s="10"/>
+      <c r="E126" s="11"/>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="23" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9">
+      <c r="B130" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="5"/>
+    </row>
+    <row r="131" spans="2:9">
+      <c r="B131" s="6"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="8"/>
+    </row>
+    <row r="132" spans="2:9">
+      <c r="B132" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="8"/>
+      <c r="I132" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9">
+      <c r="B133" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="8"/>
+      <c r="I133" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9">
+      <c r="B134" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="8"/>
+    </row>
+    <row r="135" spans="2:9">
+      <c r="B135" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="8"/>
+      <c r="G135" s="158" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I135" s="158" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9">
+      <c r="B136" s="6"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="8"/>
+      <c r="G136" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I136" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="137" spans="2:9">
+      <c r="B137" s="167" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="8"/>
+      <c r="G137" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I137" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9">
+      <c r="B138" s="6"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="8"/>
+      <c r="G138" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I138" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9">
+      <c r="B139" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="8"/>
+      <c r="G139" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9">
+      <c r="B140" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="11"/>
+      <c r="G140" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9">
+      <c r="B143" s="23" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9">
+      <c r="B145" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="5"/>
+    </row>
+    <row r="146" spans="2:9">
+      <c r="B146" s="6"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="8"/>
+    </row>
+    <row r="147" spans="2:9">
+      <c r="B147" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="8"/>
+    </row>
+    <row r="148" spans="2:9">
+      <c r="B148" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="8"/>
+    </row>
+    <row r="149" spans="2:9">
+      <c r="B149" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="8"/>
+    </row>
+    <row r="150" spans="2:9">
+      <c r="B150" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="8"/>
+      <c r="G150" s="158" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I150" s="158" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9">
+      <c r="B151" s="6"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="8"/>
+      <c r="G151" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9">
+      <c r="B152" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="8"/>
+      <c r="G152" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I152" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="153" spans="2:9">
+      <c r="B153" s="6"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="8"/>
+      <c r="G153" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I153" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9">
+      <c r="B154" s="167" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="8"/>
+      <c r="G154" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I154" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="155" spans="2:9">
+      <c r="B155" s="6"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="8"/>
+      <c r="G155" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I155" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="156" spans="2:9">
+      <c r="B156" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C156" s="10"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="11"/>
+    </row>
+    <row r="157" spans="2:9">
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+    </row>
+    <row r="158" spans="2:9">
+      <c r="B158" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+    </row>
+    <row r="159" spans="2:9">
+      <c r="B159" s="23"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+    </row>
+    <row r="160" spans="2:9">
+      <c r="B160" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="5"/>
+    </row>
+    <row r="161" spans="2:9">
+      <c r="B161" s="6"/>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="8"/>
+    </row>
+    <row r="162" spans="2:9">
+      <c r="B162" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="8"/>
+    </row>
+    <row r="163" spans="2:9">
+      <c r="B163" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="8"/>
+    </row>
+    <row r="164" spans="2:9">
+      <c r="B164" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="8"/>
+    </row>
+    <row r="165" spans="2:9">
+      <c r="B165" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="8"/>
+    </row>
+    <row r="166" spans="2:9">
+      <c r="B166" s="6"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="8"/>
+    </row>
+    <row r="167" spans="2:9">
+      <c r="B167" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="8"/>
+      <c r="G167" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I167" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="168" spans="2:9">
+      <c r="B168" s="6"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="8"/>
+      <c r="G168" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I168" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9">
+      <c r="B169" s="154" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="8"/>
+      <c r="G169" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I169" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="170" spans="2:9">
+      <c r="B170" s="6"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="8"/>
+      <c r="G170" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I170" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="171" spans="2:9">
+      <c r="B171" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C171" s="10"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="11"/>
+      <c r="G171" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I171" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="172" spans="2:9">
+      <c r="B172" s="23"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+    </row>
+    <row r="174" spans="2:9">
+      <c r="B174" s="23" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9">
+      <c r="B176" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="5"/>
+    </row>
+    <row r="177" spans="2:9">
+      <c r="B177" s="6"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="8"/>
+    </row>
+    <row r="178" spans="2:9">
+      <c r="B178" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="8"/>
+    </row>
+    <row r="179" spans="2:9">
+      <c r="B179" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="8"/>
+    </row>
+    <row r="180" spans="2:9">
+      <c r="B180" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C180" s="7"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="8"/>
+    </row>
+    <row r="181" spans="2:9">
+      <c r="B181" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="8"/>
+      <c r="G181" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I181" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="182" spans="2:9">
+      <c r="B182" s="6"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="8"/>
+      <c r="G182" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I182" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9">
+      <c r="B183" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C183" s="7"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="8"/>
+      <c r="G183" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I183" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="184" spans="2:9">
+      <c r="B184" s="6"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="8"/>
+      <c r="G184" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I184" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="185" spans="2:9">
+      <c r="B185" s="154" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C185" s="7"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="8"/>
+      <c r="G185" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I185" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9">
+      <c r="B186" s="6"/>
+      <c r="C186" s="7"/>
+      <c r="D186" s="7"/>
+      <c r="E186" s="8"/>
+      <c r="G186" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I186" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9">
+      <c r="B187" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C187" s="10"/>
+      <c r="D187" s="10"/>
+      <c r="E187" s="11"/>
+    </row>
+    <row r="189" spans="2:9">
+      <c r="B189" s="23" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="191" spans="2:9">
+      <c r="B191" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="5"/>
+    </row>
+    <row r="192" spans="2:9">
+      <c r="B192" s="6"/>
+      <c r="C192" s="7"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="8"/>
+    </row>
+    <row r="193" spans="2:9">
+      <c r="B193" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C193" s="7"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="8"/>
+    </row>
+    <row r="194" spans="2:9">
+      <c r="B194" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C194" s="7"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="8"/>
+    </row>
+    <row r="195" spans="2:9">
+      <c r="B195" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C195" s="7"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="8"/>
+    </row>
+    <row r="196" spans="2:9">
+      <c r="B196" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C196" s="7"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="8"/>
+    </row>
+    <row r="197" spans="2:9">
+      <c r="B197" s="6"/>
+      <c r="C197" s="7"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="8"/>
+      <c r="G197" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9">
+      <c r="B198" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C198" s="7"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="8"/>
+      <c r="G198" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I198" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9">
+      <c r="B199" s="6"/>
+      <c r="C199" s="7"/>
+      <c r="D199" s="7"/>
+      <c r="E199" s="8"/>
+      <c r="G199" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I199" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9">
+      <c r="B200" s="154" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C200" s="7"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="8"/>
+      <c r="G200" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I200" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9">
+      <c r="B201" s="6"/>
+      <c r="C201" s="7"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="8"/>
+      <c r="G201" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I201" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9">
+      <c r="B202" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C202" s="10"/>
+      <c r="D202" s="10"/>
+      <c r="E202" s="11"/>
+      <c r="G202" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I202" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9">
+      <c r="B205" s="23" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9">
+      <c r="B206" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C206" s="4"/>
+      <c r="D206" s="4"/>
+      <c r="E206" s="5"/>
+    </row>
+    <row r="207" spans="2:9">
+      <c r="B207" s="6"/>
+      <c r="C207" s="7"/>
+      <c r="D207" s="7"/>
+      <c r="E207" s="8"/>
+    </row>
+    <row r="208" spans="2:9">
+      <c r="B208" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C208" s="7"/>
+      <c r="D208" s="7"/>
+      <c r="E208" s="8"/>
+    </row>
+    <row r="209" spans="2:9">
+      <c r="B209" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C209" s="7"/>
+      <c r="D209" s="7"/>
+      <c r="E209" s="8"/>
+    </row>
+    <row r="210" spans="2:9">
+      <c r="B210" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C210" s="7"/>
+      <c r="D210" s="7"/>
+      <c r="E210" s="8"/>
+      <c r="G210" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I210" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9">
+      <c r="B211" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7"/>
+      <c r="E211" s="8"/>
+    </row>
+    <row r="212" spans="2:9">
+      <c r="B212" s="6"/>
+      <c r="C212" s="7"/>
+      <c r="D212" s="7"/>
+      <c r="E212" s="8"/>
+      <c r="G212" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I212" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9">
+      <c r="B213" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C213" s="7"/>
+      <c r="D213" s="7"/>
+      <c r="E213" s="8"/>
+      <c r="G213" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I213" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9">
+      <c r="B214" s="6"/>
+      <c r="C214" s="7"/>
+      <c r="D214" s="7"/>
+      <c r="E214" s="8"/>
+      <c r="G214" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I214" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="215" spans="2:9">
+      <c r="B215" s="154" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C215" s="7"/>
+      <c r="D215" s="7"/>
+      <c r="E215" s="8"/>
+      <c r="G215" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="216" spans="2:9">
+      <c r="B216" s="6"/>
+      <c r="C216" s="7"/>
+      <c r="D216" s="7"/>
+      <c r="E216" s="8"/>
+      <c r="G216" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="217" spans="2:9">
+      <c r="B217" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C217" s="10"/>
+      <c r="D217" s="10"/>
+      <c r="E217" s="11"/>
+    </row>
+    <row r="219" spans="2:9">
+      <c r="B219" s="23" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="220" spans="2:9">
+      <c r="B220" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C220" s="4"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="5"/>
+    </row>
+    <row r="221" spans="2:9">
+      <c r="B221" s="6"/>
+      <c r="C221" s="7"/>
+      <c r="D221" s="7"/>
+      <c r="E221" s="7"/>
+      <c r="F221" s="8"/>
+    </row>
+    <row r="222" spans="2:9">
+      <c r="B222" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C222" s="7"/>
+      <c r="D222" s="7"/>
+      <c r="E222" s="7"/>
+      <c r="F222" s="8"/>
+    </row>
+    <row r="223" spans="2:9">
+      <c r="B223" s="167" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C223" s="7"/>
+      <c r="D223" s="7"/>
+      <c r="E223" s="7"/>
+      <c r="F223" s="8"/>
+    </row>
+    <row r="224" spans="2:9">
+      <c r="B224" s="6"/>
+      <c r="C224" s="7"/>
+      <c r="D224" s="7"/>
+      <c r="E224" s="7"/>
+      <c r="F224" s="8"/>
+    </row>
+    <row r="225" spans="2:6">
+      <c r="B225" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C225" s="7"/>
+      <c r="D225" s="7"/>
+      <c r="E225" s="7"/>
+      <c r="F225" s="8"/>
+    </row>
+    <row r="226" spans="2:6">
+      <c r="B226" s="167" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C226" s="7"/>
+      <c r="D226" s="7"/>
+      <c r="E226" s="7"/>
+      <c r="F226" s="8"/>
+    </row>
+    <row r="227" spans="2:6">
+      <c r="B227" s="6" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C227" s="7"/>
+      <c r="D227" s="7"/>
+      <c r="E227" s="7"/>
+      <c r="F227" s="8"/>
+    </row>
+    <row r="228" spans="2:6">
+      <c r="B228" s="6" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C228" s="7"/>
+      <c r="D228" s="7"/>
+      <c r="E228" s="7"/>
+      <c r="F228" s="8"/>
+    </row>
+    <row r="229" spans="2:6">
+      <c r="B229" s="6" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C229" s="7"/>
+      <c r="D229" s="7"/>
+      <c r="E229" s="7"/>
+      <c r="F229" s="8"/>
+    </row>
+    <row r="230" spans="2:6">
+      <c r="B230" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C230" s="7"/>
+      <c r="D230" s="7"/>
+      <c r="E230" s="7"/>
+      <c r="F230" s="8"/>
+    </row>
+    <row r="231" spans="2:6">
+      <c r="B231" s="6"/>
+      <c r="C231" s="7"/>
+      <c r="D231" s="7"/>
+      <c r="E231" s="7"/>
+      <c r="F231" s="8"/>
+    </row>
+    <row r="232" spans="2:6">
+      <c r="B232" s="6" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C232" s="7"/>
+      <c r="D232" s="7"/>
+      <c r="E232" s="7"/>
+      <c r="F232" s="8"/>
+    </row>
+    <row r="233" spans="2:6">
+      <c r="B233" s="6" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C233" s="7"/>
+      <c r="D233" s="7"/>
+      <c r="E233" s="7"/>
+      <c r="F233" s="8"/>
+    </row>
+    <row r="234" spans="2:6">
+      <c r="B234" s="6"/>
+      <c r="C234" s="7"/>
+      <c r="D234" s="7"/>
+      <c r="E234" s="7"/>
+      <c r="F234" s="8"/>
+    </row>
+    <row r="235" spans="2:6">
+      <c r="B235" s="6" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C235" s="7"/>
+      <c r="D235" s="7"/>
+      <c r="E235" s="7"/>
+      <c r="F235" s="8"/>
+    </row>
+    <row r="236" spans="2:6">
+      <c r="B236" s="6" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C236" s="7"/>
+      <c r="D236" s="7"/>
+      <c r="E236" s="7"/>
+      <c r="F236" s="8"/>
+    </row>
+    <row r="237" spans="2:6">
+      <c r="B237" s="6"/>
+      <c r="C237" s="7"/>
+      <c r="D237" s="7"/>
+      <c r="E237" s="7"/>
+      <c r="F237" s="8"/>
+    </row>
+    <row r="238" spans="2:6">
+      <c r="B238" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C238" s="7"/>
+      <c r="D238" s="7"/>
+      <c r="E238" s="7"/>
+      <c r="F238" s="8"/>
+    </row>
+    <row r="239" spans="2:6">
+      <c r="B239" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C239" s="7"/>
+      <c r="D239" s="7"/>
+      <c r="E239" s="7"/>
+      <c r="F239" s="8"/>
+    </row>
+    <row r="240" spans="2:6">
+      <c r="B240" s="6"/>
+      <c r="C240" s="7"/>
+      <c r="D240" s="7"/>
+      <c r="E240" s="7"/>
+      <c r="F240" s="8"/>
+    </row>
+    <row r="241" spans="2:9">
+      <c r="B241" s="6" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C241" s="7"/>
+      <c r="D241" s="7"/>
+      <c r="E241" s="7"/>
+      <c r="F241" s="8"/>
+    </row>
+    <row r="242" spans="2:9">
+      <c r="B242" s="9" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C242" s="10"/>
+      <c r="D242" s="10"/>
+      <c r="E242" s="10"/>
+      <c r="F242" s="11"/>
+    </row>
+    <row r="244" spans="2:9">
+      <c r="B244" s="23" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9">
+      <c r="B246" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C246" s="4"/>
+      <c r="D246" s="4"/>
+      <c r="E246" s="5"/>
+    </row>
+    <row r="247" spans="2:9">
+      <c r="B247" s="6"/>
+      <c r="C247" s="7"/>
+      <c r="D247" s="7"/>
+      <c r="E247" s="8"/>
+    </row>
+    <row r="248" spans="2:9">
+      <c r="B248" s="167" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C248" s="7"/>
+      <c r="D248" s="7"/>
+      <c r="E248" s="8"/>
+    </row>
+    <row r="249" spans="2:9">
+      <c r="B249" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C249" s="7"/>
+      <c r="D249" s="7"/>
+      <c r="E249" s="8"/>
+    </row>
+    <row r="250" spans="2:9">
+      <c r="B250" s="6" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C250" s="7"/>
+      <c r="D250" s="7"/>
+      <c r="E250" s="8"/>
+      <c r="G250" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I250" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9">
+      <c r="B251" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C251" s="7"/>
+      <c r="D251" s="7"/>
+      <c r="E251" s="8"/>
+    </row>
+    <row r="252" spans="2:9">
+      <c r="B252" s="6"/>
+      <c r="C252" s="7"/>
+      <c r="D252" s="7"/>
+      <c r="E252" s="8"/>
+      <c r="G252" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I252" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="253" spans="2:9">
+      <c r="B253" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C253" s="7"/>
+      <c r="D253" s="7"/>
+      <c r="E253" s="8"/>
+      <c r="G253" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I253" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="254" spans="2:9">
+      <c r="B254" s="6"/>
+      <c r="C254" s="7"/>
+      <c r="D254" s="7"/>
+      <c r="E254" s="8"/>
+      <c r="G254" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I254" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9">
+      <c r="B255" s="154" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C255" s="7"/>
+      <c r="D255" s="7"/>
+      <c r="E255" s="8"/>
+      <c r="G255" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I255" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="256" spans="2:9">
+      <c r="B256" s="6"/>
+      <c r="C256" s="7"/>
+      <c r="D256" s="7"/>
+      <c r="E256" s="8"/>
+      <c r="G256" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I256" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="257" spans="2:5">
+      <c r="B257" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C257" s="10"/>
+      <c r="D257" s="10"/>
+      <c r="E257" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>